--- a/output/reports/cv_experiment_Stacking_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_qcut_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>147.3877637386322</v>
+        <v>1.09474515914917</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8848774569771193</v>
+        <v>0.9934911333772632</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8973904231061566</v>
+        <v>0.9675324675324676</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8966414074616869</v>
+        <v>0.9672994436658597</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9621199439958255</v>
+        <v>0.9986424571525538</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>202.4163522720337</v>
+        <v>0.9859244823455811</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8898315700176177</v>
+        <v>0.9934903405912376</v>
       </c>
       <c r="F3" t="n">
-        <v>0.896883709146187</v>
+        <v>0.9675324675324676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8961309946590286</v>
+        <v>0.9672994436658597</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9622568545699719</v>
+        <v>0.9986424571525538</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>147.3877637386322</v>
+        <v>1.09474515914917</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8848774569771193</v>
+        <v>0.9934911333772632</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8973904231061566</v>
+        <v>0.9675324675324676</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8966414074616869</v>
+        <v>0.9672994436658597</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9621199439958255</v>
+        <v>0.9986424571525538</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>202.4163522720337</v>
+        <v>0.9859244823455811</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8898315700176177</v>
+        <v>0.9934903405912376</v>
       </c>
       <c r="F3" t="n">
-        <v>0.896883709146187</v>
+        <v>0.9675324675324676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8961309946590286</v>
+        <v>0.9672994436658597</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9622568545699719</v>
+        <v>0.9986424571525538</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Stacking_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_Stacking_qcut_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.09474515914917</v>
+        <v>1.91798996925354</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9934911333772632</v>
+        <v>0.6226746192510823</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9675324675324676</v>
+        <v>0.7584745762711864</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9672994436658597</v>
+        <v>0.7282187468264446</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9986424571525538</v>
+        <v>0.9155774202815282</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9859244823455811</v>
+        <v>2.392696142196655</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9934903405912376</v>
+        <v>0.6481229339073995</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9675324675324676</v>
+        <v>0.7584745762711864</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9672994436658597</v>
+        <v>0.7282187468264446</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9986424571525538</v>
+        <v>0.9155774202815282</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.09474515914917</v>
+        <v>1.91798996925354</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9934911333772632</v>
+        <v>0.6226746192510823</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9675324675324676</v>
+        <v>0.7584745762711864</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9672994436658597</v>
+        <v>0.7282187468264446</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9986424571525538</v>
+        <v>0.9155774202815282</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9859244823455811</v>
+        <v>2.392696142196655</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9934903405912376</v>
+        <v>0.6481229339073995</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9675324675324676</v>
+        <v>0.7584745762711864</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9672994436658597</v>
+        <v>0.7282187468264446</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9986424571525538</v>
+        <v>0.9155774202815282</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
